--- a/Data/PayIn_PayOut.xlsx
+++ b/Data/PayIn_PayOut.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E41F5C-3D83-4C53-B8CD-59C7B251641B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{117407C3-746A-4C36-A0AA-9D9E6B8D5926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pay_In_Request" sheetId="1" r:id="rId1"/>
     <sheet name="Pay_Out_Request" sheetId="2" r:id="rId2"/>
+    <sheet name="Pay_In_Release" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="10">
   <si>
     <t>fileFormat</t>
   </si>
@@ -406,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
@@ -439,14 +440,24 @@
       <c r="B2" s="1">
         <v>11</v>
       </c>
-      <c r="C2" s="1">
-        <v>43562789027</v>
+      <c r="C2" s="3">
+        <v>11162025013</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C5" s="1">
+        <v>11922025908</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C6">
+        <v>11162025013</v>
       </c>
     </row>
   </sheetData>
@@ -478,8 +489,8 @@
       <c r="A2" s="3">
         <v>11</v>
       </c>
-      <c r="B2" s="3">
-        <v>43562789027</v>
+      <c r="B2">
+        <v>11162025013</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>9</v>
@@ -492,12 +503,16 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
+      <c r="B4">
+        <v>11162025013</v>
+      </c>
       <c r="C4" s="3"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
+      <c r="B5" s="3">
+        <v>11922025908</v>
+      </c>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -523,4 +538,40 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43BC3320-C84D-4C52-BC34-70FCB7E17342}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>11</v>
+      </c>
+      <c r="B2" s="3">
+        <v>11162025013</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Data/PayIn_PayOut.xlsx
+++ b/Data/PayIn_PayOut.xlsx
@@ -8,19 +8,30 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{117407C3-746A-4C36-A0AA-9D9E6B8D5926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99F2F346-F04D-478B-90B3-68C42DDEB85E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19725" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pay_In_Request" sheetId="1" r:id="rId1"/>
     <sheet name="Pay_Out_Request" sheetId="2" r:id="rId2"/>
     <sheet name="Pay_In_Release" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -441,7 +452,7 @@
         <v>11</v>
       </c>
       <c r="C2" s="3">
-        <v>11162025013</v>
+        <v>11922026133</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>6</v>
@@ -490,7 +501,7 @@
         <v>11</v>
       </c>
       <c r="B2">
-        <v>11162025013</v>
+        <v>11922026133</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>9</v>
@@ -503,16 +514,11 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
-      <c r="B4">
-        <v>11162025013</v>
-      </c>
       <c r="C4" s="3"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
-      <c r="B5" s="3">
-        <v>11922025908</v>
-      </c>
+      <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
